--- a/src_files/data_files/industrialCHP.xlsx
+++ b/src_files/data_files/industrialCHP.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C48E239-DA5C-4345-804C-857F2B6CE868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E523FC-77B3-413F-8437-B871745C60B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18120" yWindow="-105" windowWidth="18240" windowHeight="28320" tabRatio="799" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="799" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unitdata" sheetId="8" r:id="rId1"/>
     <sheet name="demanddata" sheetId="7" r:id="rId2"/>
-    <sheet name="storagedata" sheetId="10" r:id="rId3"/>
+    <sheet name="nodedata" sheetId="10" r:id="rId3"/>
     <sheet name="Summary" sheetId="4" r:id="rId4"/>
     <sheet name="H2Heavy, capacities" sheetId="1" r:id="rId5"/>
     <sheet name="H2Heavy, demands" sheetId="2" r:id="rId6"/>
@@ -23,7 +23,7 @@
     <sheet name="Eurostat" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">storagedata!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">nodedata!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="130">
   <si>
     <t>Country</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>method</t>
+  </si>
+  <si>
+    <t>nodeBalance</t>
   </si>
 </sst>
 </file>
@@ -949,7 +952,10 @@
     <cellStyle name="Normal 3" xfId="1" xr:uid="{B922DAB1-96BE-4C47-ACB7-A4E9C8932980}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="26">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1280,40 +1286,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{53CAE17E-E130-454C-A23D-D1F2C5367D34}" name="Table2" displayName="Table2" ref="A1:J24" totalsRowShown="0" headerRowDxfId="24">
-  <autoFilter ref="A1:J24" xr:uid="{618B6211-7040-488C-9F85-846A32BD1FFB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{53CAE17E-E130-454C-A23D-D1F2C5367D34}" name="Table2" displayName="Table2" ref="A1:K24" totalsRowShown="0" headerRowDxfId="25">
+  <autoFilter ref="A1:K24" xr:uid="{618B6211-7040-488C-9F85-846A32BD1FFB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
     <sortCondition ref="B1:B24"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{FD66C488-929A-4E40-97B9-698BE28209C7}" name="Country" dataDxfId="23"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{FD66C488-929A-4E40-97B9-698BE28209C7}" name="Country" dataDxfId="24"/>
     <tableColumn id="2" xr3:uid="{04387B0B-A6A1-47CC-82EB-6B34AE82821B}" name="Grid"/>
     <tableColumn id="3" xr3:uid="{57483FE3-C6A9-426F-9DF7-4926168CE122}" name="Node_suffix"/>
-    <tableColumn id="4" xr3:uid="{F155858A-1910-4203-8242-FCFC753CE0F1}" name="Scenario" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{2976D6D8-21B5-4358-9605-474352CC3FAF}" name="Year" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{894F3647-7759-4FB2-B8B6-24582E443654}" name="upwardLimit" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{622B05A3-F0D0-4BEE-B5E5-8AA1239444AE}" name="reference" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{FB556C05-FAE9-43E0-9FC0-D26AB24EC6BC}" name="balancePenalty" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{7EAD7D20-CDA2-446F-BC00-8EC30C32C13B}" name="selfDischargeLoss" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{078F1241-6AF8-480F-897B-1DA7DB1520F6}" name="maxSpill" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{F155858A-1910-4203-8242-FCFC753CE0F1}" name="Scenario" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{2976D6D8-21B5-4358-9605-474352CC3FAF}" name="Year" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{5D7C3B58-23CE-4BD9-9814-7BCAEB987C3B}" name="nodeBalance" dataDxfId="0" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{894F3647-7759-4FB2-B8B6-24582E443654}" name="upwardLimit" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{622B05A3-F0D0-4BEE-B5E5-8AA1239444AE}" name="reference" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{FB556C05-FAE9-43E0-9FC0-D26AB24EC6BC}" name="balancePenalty" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{7EAD7D20-CDA2-446F-BC00-8EC30C32C13B}" name="selfDischargeLoss" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{078F1241-6AF8-480F-897B-1DA7DB1520F6}" name="maxSpill" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{20DC892E-7082-4467-928B-8F4B2C671031}" name="Table1" displayName="Table1" ref="A1:I28" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{20DC892E-7082-4467-928B-8F4B2C671031}" name="Table1" displayName="Table1" ref="A1:I28" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="A1:I28" xr:uid="{20DC892E-7082-4467-928B-8F4B2C671031}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{90B3BA90-E856-467E-A12E-718C92D72014}" name="Country" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{47E364C8-C977-4369-A805-4B42B4F3422D}" name="Generator_ID" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{D50F5294-47D2-4C56-800B-3E44FF430FA7}" name="Scenario" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{649C99FE-77E1-437E-9EDE-D888843F1482}" name="Year" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{1A49AF74-6C24-40D6-B37A-D2ADAB4DE02B}" name="capacity_input1" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{F30D702A-E7C4-4705-81A5-A391EA397049}" name="capacity_output1" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{B74AC38E-95FA-433D-B521-50231B26F101}" name="node_suffix_output2" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{2E1D1700-DA32-4625-8DFD-E756415F2202}" name="capacity_output2" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{89275BD6-4B5C-4E77-BA1F-FF40DDEF4E2A}" name="Note" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{90B3BA90-E856-467E-A12E-718C92D72014}" name="Country" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{47E364C8-C977-4369-A805-4B42B4F3422D}" name="Generator_ID" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{D50F5294-47D2-4C56-800B-3E44FF430FA7}" name="Scenario" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{649C99FE-77E1-437E-9EDE-D888843F1482}" name="Year" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{1A49AF74-6C24-40D6-B37A-D2ADAB4DE02B}" name="capacity_input1" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{F30D702A-E7C4-4705-81A5-A391EA397049}" name="capacity_output1" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{B74AC38E-95FA-433D-B521-50231B26F101}" name="node_suffix_output2" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{2E1D1700-DA32-4625-8DFD-E756415F2202}" name="capacity_output2" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{89275BD6-4B5C-4E77-BA1F-FF40DDEF4E2A}" name="Note" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3594,12 +3601,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A17 G5:G17 B5:F23">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:G4">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3612,22 +3619,22 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="58"/>
     <col min="2" max="3" width="19.7109375" style="58" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" style="59" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="59"/>
-    <col min="6" max="6" width="16.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="62" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" style="62" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" style="62" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.5703125" style="62"/>
+    <col min="5" max="6" width="11.5703125" style="59"/>
+    <col min="7" max="7" width="16.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="62" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" style="62" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.5703125" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
@@ -3644,22 +3651,25 @@
         <v>3</v>
       </c>
       <c r="F1" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="H1" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="I1" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="J1" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="K1" s="61" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="62" t="s">
         <v>106</v>
       </c>
@@ -3675,14 +3685,17 @@
       <c r="E2" s="59">
         <v>1</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63">
+      <c r="F2" s="59">
+        <v>1</v>
+      </c>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63">
         <v>4000</v>
       </c>
-      <c r="I2" s="63"/>
       <c r="J2" s="63"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K2" s="63"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="62" t="s">
         <v>15</v>
       </c>
@@ -3698,14 +3711,17 @@
       <c r="E3" s="59">
         <v>1</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63">
+      <c r="F3" s="59">
+        <v>1</v>
+      </c>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63">
         <v>4000</v>
       </c>
-      <c r="I3" s="63"/>
       <c r="J3" s="63"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3" s="63"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="62" t="s">
         <v>127</v>
       </c>
@@ -3721,14 +3737,17 @@
       <c r="E4" s="59">
         <v>1</v>
       </c>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63">
+      <c r="F4" s="59">
+        <v>1</v>
+      </c>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63">
         <v>4000</v>
       </c>
-      <c r="I4" s="63"/>
       <c r="J4" s="63"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4" s="63"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="62" t="s">
         <v>9</v>
       </c>
@@ -3744,14 +3763,17 @@
       <c r="E5" s="59">
         <v>1</v>
       </c>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63">
+      <c r="F5" s="59">
+        <v>1</v>
+      </c>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63">
         <v>4000</v>
       </c>
-      <c r="I5" s="63"/>
       <c r="J5" s="63"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K5" s="63"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="62" t="s">
         <v>112</v>
       </c>
@@ -3767,14 +3789,17 @@
       <c r="E6" s="59">
         <v>1</v>
       </c>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63">
+      <c r="F6" s="59">
+        <v>1</v>
+      </c>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63">
         <v>4000</v>
       </c>
-      <c r="I6" s="63"/>
       <c r="J6" s="63"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K6" s="63"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="62" t="s">
         <v>19</v>
       </c>
@@ -3790,14 +3815,17 @@
       <c r="E7" s="59">
         <v>1</v>
       </c>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63">
+      <c r="F7" s="59">
+        <v>1</v>
+      </c>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63">
         <v>4000</v>
       </c>
-      <c r="I7" s="63"/>
       <c r="J7" s="63"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K7" s="63"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="62" t="s">
         <v>25</v>
       </c>
@@ -3813,14 +3841,17 @@
       <c r="E8" s="59">
         <v>1</v>
       </c>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63">
+      <c r="F8" s="59">
+        <v>1</v>
+      </c>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63">
         <v>4000</v>
       </c>
-      <c r="I8" s="63"/>
       <c r="J8" s="63"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K8" s="63"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="62" t="s">
         <v>12</v>
       </c>
@@ -3836,14 +3867,17 @@
       <c r="E9" s="59">
         <v>1</v>
       </c>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63">
+      <c r="F9" s="59">
+        <v>1</v>
+      </c>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63">
         <v>4000</v>
       </c>
-      <c r="I9" s="63"/>
       <c r="J9" s="63"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K9" s="63"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="62" t="s">
         <v>20</v>
       </c>
@@ -3859,14 +3893,17 @@
       <c r="E10" s="59">
         <v>1</v>
       </c>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63">
+      <c r="F10" s="59">
+        <v>1</v>
+      </c>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63">
         <v>4000</v>
       </c>
-      <c r="I10" s="63"/>
       <c r="J10" s="63"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K10" s="63"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="62" t="s">
         <v>10</v>
       </c>
@@ -3882,14 +3919,17 @@
       <c r="E11" s="59">
         <v>1</v>
       </c>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63">
+      <c r="F11" s="59">
+        <v>1</v>
+      </c>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63">
         <v>4000</v>
       </c>
-      <c r="I11" s="63"/>
       <c r="J11" s="63"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K11" s="63"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="62" t="s">
         <v>23</v>
       </c>
@@ -3905,14 +3945,17 @@
       <c r="E12" s="59">
         <v>1</v>
       </c>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63">
+      <c r="F12" s="59">
+        <v>1</v>
+      </c>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63">
         <v>4000</v>
       </c>
-      <c r="I12" s="63"/>
       <c r="J12" s="63"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K12" s="63"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="62" t="s">
         <v>24</v>
       </c>
@@ -3928,14 +3971,17 @@
       <c r="E13" s="59">
         <v>1</v>
       </c>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63">
+      <c r="F13" s="59">
+        <v>1</v>
+      </c>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63">
         <v>4000</v>
       </c>
-      <c r="I13" s="63"/>
       <c r="J13" s="63"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K13" s="63"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="62" t="s">
         <v>14</v>
       </c>
@@ -3951,14 +3997,17 @@
       <c r="E14" s="59">
         <v>1</v>
       </c>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63">
+      <c r="F14" s="59">
+        <v>1</v>
+      </c>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63">
         <v>4000</v>
       </c>
-      <c r="I14" s="63"/>
       <c r="J14" s="63"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K14" s="63"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="62" t="s">
         <v>21</v>
       </c>
@@ -3974,14 +4023,17 @@
       <c r="E15" s="59">
         <v>1</v>
       </c>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63">
+      <c r="F15" s="59">
+        <v>1</v>
+      </c>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63">
         <v>4000</v>
       </c>
-      <c r="I15" s="63"/>
       <c r="J15" s="63"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K15" s="63"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="62" t="s">
         <v>27</v>
       </c>
@@ -3997,14 +4049,17 @@
       <c r="E16" s="59">
         <v>1</v>
       </c>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63">
+      <c r="F16" s="59">
+        <v>1</v>
+      </c>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63">
         <v>4000</v>
       </c>
-      <c r="I16" s="63"/>
       <c r="J16" s="63"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K16" s="63"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="62" t="s">
         <v>22</v>
       </c>
@@ -4020,14 +4075,17 @@
       <c r="E17" s="59">
         <v>1</v>
       </c>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63">
+      <c r="F17" s="59">
+        <v>1</v>
+      </c>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63">
         <v>4000</v>
       </c>
-      <c r="I17" s="63"/>
       <c r="J17" s="63"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K17" s="63"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="62" t="s">
         <v>13</v>
       </c>
@@ -4043,14 +4101,17 @@
       <c r="E18" s="59">
         <v>1</v>
       </c>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63">
+      <c r="F18" s="59">
+        <v>1</v>
+      </c>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63">
         <v>4000</v>
       </c>
-      <c r="I18" s="63"/>
       <c r="J18" s="63"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K18" s="63"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="62" t="s">
         <v>26</v>
       </c>
@@ -4066,14 +4127,17 @@
       <c r="E19" s="59">
         <v>1</v>
       </c>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63">
+      <c r="F19" s="59">
+        <v>1</v>
+      </c>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63">
         <v>4000</v>
       </c>
-      <c r="I19" s="63"/>
       <c r="J19" s="63"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K19" s="63"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="62" t="s">
         <v>16</v>
       </c>
@@ -4089,14 +4153,17 @@
       <c r="E20" s="59">
         <v>1</v>
       </c>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63">
+      <c r="F20" s="59">
+        <v>1</v>
+      </c>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63">
         <v>4000</v>
       </c>
-      <c r="I20" s="63"/>
       <c r="J20" s="63"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K20" s="63"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="62" t="s">
         <v>17</v>
       </c>
@@ -4112,14 +4179,17 @@
       <c r="E21" s="59">
         <v>1</v>
       </c>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63">
+      <c r="F21" s="59">
+        <v>1</v>
+      </c>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63">
         <v>4000</v>
       </c>
-      <c r="I21" s="63"/>
       <c r="J21" s="63"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K21" s="63"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="62" t="s">
         <v>18</v>
       </c>
@@ -4135,14 +4205,17 @@
       <c r="E22" s="59">
         <v>1</v>
       </c>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63">
+      <c r="F22" s="59">
+        <v>1</v>
+      </c>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63">
         <v>4000</v>
       </c>
-      <c r="I22" s="63"/>
       <c r="J22" s="63"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K22" s="63"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="62" t="s">
         <v>11</v>
       </c>
@@ -4158,19 +4231,22 @@
       <c r="E23" s="59">
         <v>1</v>
       </c>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63">
+      <c r="F23" s="59">
+        <v>1</v>
+      </c>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63">
         <v>4000</v>
       </c>
-      <c r="I23" s="63"/>
       <c r="J23" s="63"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K23" s="63"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="62"/>
-      <c r="G24" s="63"/>
       <c r="H24" s="63"/>
       <c r="I24" s="63"/>
       <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -7241,7 +7317,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I28">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7572,7 +7648,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:G15">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
